--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4039,48 +4039,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135323935</v>
+        <v>135323533</v>
       </c>
       <c r="B32" t="n">
-        <v>96678</v>
+        <v>91896</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2166</v>
+        <v>3242</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619433</v>
+        <v>619556</v>
       </c>
       <c r="R32" t="n">
-        <v>7322100</v>
+        <v>7322012</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4130,64 +4130,84 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135323533</v>
+        <v>135322200</v>
       </c>
       <c r="B33" t="n">
-        <v>91896</v>
+        <v>91937</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619556</v>
+        <v>619552</v>
       </c>
       <c r="R33" t="n">
-        <v>7322012</v>
+        <v>7322009</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4216,7 +4236,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4226,7 +4246,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4237,43 +4257,27 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135322200</v>
+        <v>135322204</v>
       </c>
       <c r="B34" t="n">
         <v>91937</v>
@@ -4308,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619552</v>
+        <v>619650</v>
       </c>
       <c r="R34" t="n">
-        <v>7322009</v>
+        <v>7322160</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4343,7 +4347,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4353,7 +4357,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4384,7 +4388,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135322204</v>
+        <v>135323531</v>
       </c>
       <c r="B35" t="n">
         <v>91937</v>
@@ -4415,17 +4419,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619650</v>
+        <v>619624</v>
       </c>
       <c r="R35" t="n">
-        <v>7322160</v>
+        <v>7322025</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4454,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4464,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4479,64 +4483,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135323531</v>
+        <v>135325580</v>
       </c>
       <c r="B36" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619624</v>
+        <v>619647</v>
       </c>
       <c r="R36" t="n">
-        <v>7322025</v>
+        <v>7322062</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4590,19 +4590,23 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325580</v>
+        <v>135325595</v>
       </c>
       <c r="B37" t="n">
         <v>79373</v>
@@ -4637,10 +4641,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619647</v>
+        <v>619537</v>
       </c>
       <c r="R37" t="n">
-        <v>7322062</v>
+        <v>7322086</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4672,7 +4676,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4682,7 +4686,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4713,48 +4717,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135325595</v>
+        <v>135326505</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79397</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619537</v>
+        <v>619507</v>
       </c>
       <c r="R38" t="n">
-        <v>7322086</v>
+        <v>7322024</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4783,7 +4787,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4793,7 +4797,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4808,12 +4812,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4824,48 +4828,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135326505</v>
+        <v>135321361</v>
       </c>
       <c r="B39" t="n">
-        <v>79397</v>
+        <v>78776</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619507</v>
+        <v>619595</v>
       </c>
       <c r="R39" t="n">
-        <v>7322024</v>
+        <v>7322144</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4894,7 +4898,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4904,7 +4908,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4919,12 +4923,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4935,7 +4939,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135321361</v>
+        <v>135321364</v>
       </c>
       <c r="B40" t="n">
         <v>78776</v>
@@ -4970,13 +4974,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619595</v>
+        <v>619580</v>
       </c>
       <c r="R40" t="n">
-        <v>7322144</v>
+        <v>7322118</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5005,7 +5009,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5015,7 +5019,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5046,7 +5050,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135321364</v>
+        <v>135323135</v>
       </c>
       <c r="B41" t="n">
         <v>78776</v>
@@ -5077,17 +5081,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619580</v>
+        <v>619656</v>
       </c>
       <c r="R41" t="n">
-        <v>7322118</v>
+        <v>7322137</v>
       </c>
       <c r="S41" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5116,7 +5120,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5126,7 +5130,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5141,12 +5145,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5157,7 +5161,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135323135</v>
+        <v>135323142</v>
       </c>
       <c r="B42" t="n">
         <v>78776</v>
@@ -5192,13 +5196,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619656</v>
+        <v>619605</v>
       </c>
       <c r="R42" t="n">
-        <v>7322137</v>
+        <v>7322191</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5227,7 +5231,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5237,7 +5241,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5268,7 +5272,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135323142</v>
+        <v>135323144</v>
       </c>
       <c r="B43" t="n">
         <v>78776</v>
@@ -5303,13 +5307,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619605</v>
+        <v>619545</v>
       </c>
       <c r="R43" t="n">
-        <v>7322191</v>
+        <v>7322155</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5338,7 +5342,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5348,7 +5352,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,7 +5383,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135323144</v>
+        <v>135325583</v>
       </c>
       <c r="B44" t="n">
         <v>78776</v>
@@ -5410,14 +5414,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619545</v>
+        <v>619639</v>
       </c>
       <c r="R44" t="n">
-        <v>7322155</v>
+        <v>7322093</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5449,7 +5453,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5459,7 +5463,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5474,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5490,7 +5494,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135325583</v>
+        <v>135326502</v>
       </c>
       <c r="B45" t="n">
         <v>78776</v>
@@ -5521,17 +5525,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619639</v>
+        <v>619511</v>
       </c>
       <c r="R45" t="n">
-        <v>7322093</v>
+        <v>7322024</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5560,7 +5564,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5570,7 +5574,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5585,12 +5589,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5601,7 +5605,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135326502</v>
+        <v>135329821</v>
       </c>
       <c r="B46" t="n">
         <v>78776</v>
@@ -5632,17 +5636,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619511</v>
+        <v>619634</v>
       </c>
       <c r="R46" t="n">
-        <v>7322024</v>
+        <v>7321974</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5671,7 +5675,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5681,7 +5685,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5696,12 +5700,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5712,7 +5716,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135329821</v>
+        <v>135329832</v>
       </c>
       <c r="B47" t="n">
         <v>78776</v>
@@ -5747,13 +5751,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619634</v>
+        <v>619546</v>
       </c>
       <c r="R47" t="n">
-        <v>7321974</v>
+        <v>7322084</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5782,7 +5786,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5792,7 +5796,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5823,7 +5827,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135329832</v>
+        <v>135330930</v>
       </c>
       <c r="B48" t="n">
         <v>78776</v>
@@ -5854,17 +5858,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619546</v>
+        <v>619612</v>
       </c>
       <c r="R48" t="n">
-        <v>7322084</v>
+        <v>7322185</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5903,7 +5907,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5918,12 +5922,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5934,10 +5938,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135330930</v>
+        <v>135323129</v>
       </c>
       <c r="B49" t="n">
-        <v>78776</v>
+        <v>83358</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5945,37 +5949,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6437</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619612</v>
+        <v>619604</v>
       </c>
       <c r="R49" t="n">
-        <v>7322185</v>
+        <v>7322043</v>
       </c>
       <c r="S49" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6004,7 +6008,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6014,7 +6018,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6029,12 +6033,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6045,7 +6049,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135323129</v>
+        <v>135325571</v>
       </c>
       <c r="B50" t="n">
         <v>83358</v>
@@ -6076,17 +6080,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619604</v>
+        <v>619631</v>
       </c>
       <c r="R50" t="n">
-        <v>7322043</v>
+        <v>7322000</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6125,7 +6129,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6140,12 +6144,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6156,7 +6160,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135325571</v>
+        <v>135325584</v>
       </c>
       <c r="B51" t="n">
         <v>83358</v>
@@ -6191,13 +6195,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619631</v>
+        <v>619575</v>
       </c>
       <c r="R51" t="n">
-        <v>7322000</v>
+        <v>7322155</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6236,7 +6240,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6267,7 +6271,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135325584</v>
+        <v>135325589</v>
       </c>
       <c r="B52" t="n">
         <v>83358</v>
@@ -6302,13 +6306,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619575</v>
+        <v>619490</v>
       </c>
       <c r="R52" t="n">
-        <v>7322155</v>
+        <v>7322171</v>
       </c>
       <c r="S52" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6337,7 +6341,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6347,7 +6351,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6378,10 +6382,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135325589</v>
+        <v>135321549</v>
       </c>
       <c r="B53" t="n">
-        <v>83358</v>
+        <v>79992</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6389,37 +6393,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619490</v>
+        <v>619576</v>
       </c>
       <c r="R53" t="n">
-        <v>7322171</v>
+        <v>7322127</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6448,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6458,7 +6462,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6473,12 +6477,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6489,7 +6493,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135321549</v>
+        <v>135322202</v>
       </c>
       <c r="B54" t="n">
         <v>79992</v>
@@ -6520,17 +6524,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>619576</v>
+        <v>619550</v>
       </c>
       <c r="R54" t="n">
-        <v>7322127</v>
+        <v>7322004</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6559,7 +6563,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6569,7 +6573,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6584,12 +6588,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6600,7 +6604,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135322202</v>
+        <v>135322205</v>
       </c>
       <c r="B55" t="n">
         <v>79992</v>
@@ -6635,10 +6639,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>619550</v>
+        <v>619648</v>
       </c>
       <c r="R55" t="n">
-        <v>7322004</v>
+        <v>7322202</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6670,7 +6674,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6680,7 +6684,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6711,7 +6715,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135322205</v>
+        <v>135323132</v>
       </c>
       <c r="B56" t="n">
         <v>79992</v>
@@ -6742,17 +6746,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>619648</v>
+        <v>619609</v>
       </c>
       <c r="R56" t="n">
-        <v>7322202</v>
+        <v>7322073</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6781,7 +6785,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6791,7 +6795,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6806,12 +6810,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6822,7 +6826,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135323132</v>
+        <v>135323145</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6857,13 +6861,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>619609</v>
+        <v>619557</v>
       </c>
       <c r="R57" t="n">
-        <v>7322073</v>
+        <v>7322144</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6892,7 +6896,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6902,7 +6906,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6933,7 +6937,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135323145</v>
+        <v>135325572</v>
       </c>
       <c r="B58" t="n">
         <v>79992</v>
@@ -6964,17 +6968,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619557</v>
+        <v>619648</v>
       </c>
       <c r="R58" t="n">
-        <v>7322144</v>
+        <v>7321997</v>
       </c>
       <c r="S58" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7003,7 +7007,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7013,7 +7017,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7028,12 +7032,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7044,7 +7048,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135325572</v>
+        <v>135325593</v>
       </c>
       <c r="B59" t="n">
         <v>79992</v>
@@ -7079,10 +7083,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>619648</v>
+        <v>619420</v>
       </c>
       <c r="R59" t="n">
-        <v>7321997</v>
+        <v>7322107</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7114,7 +7118,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7124,7 +7128,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7155,7 +7159,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135325593</v>
+        <v>135325594</v>
       </c>
       <c r="B60" t="n">
         <v>79992</v>
@@ -7190,13 +7194,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619420</v>
+        <v>619516</v>
       </c>
       <c r="R60" t="n">
-        <v>7322107</v>
+        <v>7322084</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7225,7 +7229,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7235,7 +7239,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7266,7 +7270,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135325594</v>
+        <v>135326504</v>
       </c>
       <c r="B61" t="n">
         <v>79992</v>
@@ -7297,17 +7301,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>619516</v>
+        <v>619507</v>
       </c>
       <c r="R61" t="n">
-        <v>7322084</v>
+        <v>7322024</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7336,7 +7340,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7346,7 +7350,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7361,12 +7365,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7377,7 +7381,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135326504</v>
+        <v>135329819</v>
       </c>
       <c r="B62" t="n">
         <v>79992</v>
@@ -7408,17 +7412,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>619507</v>
+        <v>619650</v>
       </c>
       <c r="R62" t="n">
-        <v>7322024</v>
+        <v>7321988</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7447,7 +7451,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7457,7 +7461,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7472,12 +7476,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7488,7 +7492,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135329819</v>
+        <v>135329831</v>
       </c>
       <c r="B63" t="n">
         <v>79992</v>
@@ -7523,13 +7527,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>619650</v>
+        <v>619545</v>
       </c>
       <c r="R63" t="n">
-        <v>7321988</v>
+        <v>7322092</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7558,7 +7562,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7568,7 +7572,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7599,48 +7603,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135329831</v>
+        <v>135325590</v>
       </c>
       <c r="B64" t="n">
-        <v>79992</v>
+        <v>80500</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619545</v>
+        <v>619458</v>
       </c>
       <c r="R64" t="n">
-        <v>7322092</v>
+        <v>7322119</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7669,7 +7673,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7679,7 +7683,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7694,12 +7698,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7710,45 +7714,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135325590</v>
+        <v>135321366</v>
       </c>
       <c r="B65" t="n">
-        <v>80500</v>
+        <v>78377</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619458</v>
+        <v>619580</v>
       </c>
       <c r="R65" t="n">
-        <v>7322119</v>
+        <v>7322117</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7780,7 +7784,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7790,7 +7794,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7805,12 +7809,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7821,7 +7825,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135321366</v>
+        <v>135323134</v>
       </c>
       <c r="B66" t="n">
         <v>78377</v>
@@ -7852,17 +7856,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619580</v>
+        <v>619656</v>
       </c>
       <c r="R66" t="n">
-        <v>7322117</v>
+        <v>7322136</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7891,7 +7895,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7901,7 +7905,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7916,12 +7920,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7932,7 +7936,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135323134</v>
+        <v>135323141</v>
       </c>
       <c r="B67" t="n">
         <v>78377</v>
@@ -7967,13 +7971,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619656</v>
+        <v>619605</v>
       </c>
       <c r="R67" t="n">
-        <v>7322136</v>
+        <v>7322191</v>
       </c>
       <c r="S67" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8002,7 +8006,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8012,7 +8016,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8043,7 +8047,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135323141</v>
+        <v>135325582</v>
       </c>
       <c r="B68" t="n">
         <v>78377</v>
@@ -8074,17 +8078,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619605</v>
+        <v>619634</v>
       </c>
       <c r="R68" t="n">
-        <v>7322191</v>
+        <v>7322092</v>
       </c>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8113,7 +8117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8123,7 +8127,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8138,12 +8142,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8154,7 +8158,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135325582</v>
+        <v>135326506</v>
       </c>
       <c r="B69" t="n">
         <v>78377</v>
@@ -8185,17 +8189,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619634</v>
+        <v>619505</v>
       </c>
       <c r="R69" t="n">
-        <v>7322092</v>
+        <v>7322017</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8224,7 +8228,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8234,7 +8238,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8249,12 +8253,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8265,10 +8269,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135326506</v>
+        <v>135321369</v>
       </c>
       <c r="B70" t="n">
-        <v>78377</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8276,37 +8280,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619505</v>
+        <v>619598</v>
       </c>
       <c r="R70" t="n">
-        <v>7322017</v>
+        <v>7322108</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8335,7 +8347,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8345,7 +8357,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8360,12 +8377,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8376,7 +8393,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135321369</v>
+        <v>135321371</v>
       </c>
       <c r="B71" t="n">
         <v>57975</v>
@@ -8419,13 +8436,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619598</v>
+        <v>619575</v>
       </c>
       <c r="R71" t="n">
-        <v>7322108</v>
+        <v>7322044</v>
       </c>
       <c r="S71" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8454,7 +8471,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8464,7 +8481,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8500,7 +8517,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135321371</v>
+        <v>135323143</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8529,24 +8546,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619575</v>
+        <v>619588</v>
       </c>
       <c r="R72" t="n">
-        <v>7322044</v>
+        <v>7322173</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8578,7 +8592,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8588,12 +8602,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8608,12 +8617,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8624,7 +8633,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135323143</v>
+        <v>135323524</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8653,21 +8662,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619588</v>
+        <v>619644</v>
       </c>
       <c r="R73" t="n">
-        <v>7322173</v>
+        <v>7321971</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8699,7 +8703,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8709,7 +8713,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8724,23 +8733,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135323524</v>
+        <v>135326508</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8769,19 +8774,24 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619644</v>
+        <v>619441</v>
       </c>
       <c r="R74" t="n">
-        <v>7321971</v>
+        <v>7322009</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8810,7 +8820,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8820,12 +8830,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack, gran</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8840,19 +8850,23 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135326508</v>
+        <v>135326509</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8883,7 +8897,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8892,10 +8906,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619441</v>
+        <v>619463</v>
       </c>
       <c r="R75" t="n">
-        <v>7322009</v>
+        <v>7321984</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8927,7 +8941,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8937,12 +8951,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8973,7 +8987,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135326509</v>
+        <v>135326510</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -9013,10 +9027,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619463</v>
+        <v>619498</v>
       </c>
       <c r="R76" t="n">
-        <v>7321984</v>
+        <v>7321987</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9048,7 +9062,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9058,7 +9072,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -9094,7 +9108,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135326510</v>
+        <v>135329836</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -9123,21 +9137,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619498</v>
+        <v>619599</v>
       </c>
       <c r="R77" t="n">
-        <v>7321987</v>
+        <v>7321991</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9169,7 +9178,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9179,12 +9188,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9199,12 +9208,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9215,7 +9224,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135329836</v>
+        <v>135330913</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9244,19 +9253,27 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619599</v>
+        <v>619674</v>
       </c>
       <c r="R78" t="n">
-        <v>7321991</v>
+        <v>7321952</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9285,7 +9302,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9295,12 +9312,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9315,12 +9332,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9331,7 +9348,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135330913</v>
+        <v>135330918</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -9364,7 +9381,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -9374,13 +9391,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>619674</v>
+        <v>619657</v>
       </c>
       <c r="R79" t="n">
-        <v>7321952</v>
+        <v>7322019</v>
       </c>
       <c r="S79" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9409,7 +9426,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9419,12 +9436,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9455,7 +9472,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135330918</v>
+        <v>135330920</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -9488,7 +9505,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9498,13 +9515,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619657</v>
+        <v>619636</v>
       </c>
       <c r="R80" t="n">
-        <v>7322019</v>
+        <v>7322057</v>
       </c>
       <c r="S80" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9533,7 +9550,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9543,12 +9560,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Spår från födosök</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9579,7 +9596,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135330920</v>
+        <v>135330921</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -9622,13 +9639,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619636</v>
+        <v>619615</v>
       </c>
       <c r="R81" t="n">
-        <v>7322057</v>
+        <v>7322104</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9657,7 +9674,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9667,12 +9684,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Spår från födosök</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9703,7 +9720,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135330921</v>
+        <v>135330922</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9736,7 +9753,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -9746,10 +9763,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619615</v>
+        <v>619616</v>
       </c>
       <c r="R82" t="n">
-        <v>7322104</v>
+        <v>7322103</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9781,7 +9798,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9791,12 +9808,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9827,7 +9844,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135330922</v>
+        <v>135330925</v>
       </c>
       <c r="B83" t="n">
         <v>57975</v>
@@ -9870,13 +9887,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619616</v>
+        <v>619617</v>
       </c>
       <c r="R83" t="n">
-        <v>7322103</v>
+        <v>7322138</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9905,7 +9922,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9915,7 +9932,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9951,7 +9968,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135330925</v>
+        <v>135330926</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -9984,7 +10001,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -9994,13 +10011,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619617</v>
+        <v>619652</v>
       </c>
       <c r="R84" t="n">
-        <v>7322138</v>
+        <v>7322160</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10029,7 +10046,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10039,12 +10056,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10075,7 +10092,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135330926</v>
+        <v>135330929</v>
       </c>
       <c r="B85" t="n">
         <v>57975</v>
@@ -10118,13 +10135,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619652</v>
+        <v>619619</v>
       </c>
       <c r="R85" t="n">
-        <v>7322160</v>
+        <v>7322169</v>
       </c>
       <c r="S85" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10153,7 +10170,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10163,7 +10180,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -10199,7 +10216,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135330929</v>
+        <v>135330931</v>
       </c>
       <c r="B86" t="n">
         <v>57975</v>
@@ -10232,7 +10249,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10242,13 +10259,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619619</v>
+        <v>619590</v>
       </c>
       <c r="R86" t="n">
-        <v>7322169</v>
+        <v>7322174</v>
       </c>
       <c r="S86" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10277,7 +10294,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10287,12 +10304,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10323,7 +10340,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135330931</v>
+        <v>135330935</v>
       </c>
       <c r="B87" t="n">
         <v>57975</v>
@@ -10366,13 +10383,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619590</v>
+        <v>619577</v>
       </c>
       <c r="R87" t="n">
-        <v>7322174</v>
+        <v>7322144</v>
       </c>
       <c r="S87" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10401,7 +10418,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10411,7 +10428,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10447,7 +10464,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135330935</v>
+        <v>135330936</v>
       </c>
       <c r="B88" t="n">
         <v>57975</v>
@@ -10490,13 +10507,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>619577</v>
+        <v>619598</v>
       </c>
       <c r="R88" t="n">
-        <v>7322144</v>
+        <v>7322107</v>
       </c>
       <c r="S88" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10525,7 +10542,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10535,7 +10552,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10571,7 +10588,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135330936</v>
+        <v>135330938</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -10614,13 +10631,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>619598</v>
+        <v>619571</v>
       </c>
       <c r="R89" t="n">
-        <v>7322107</v>
+        <v>7322045</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10649,7 +10666,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10659,7 +10676,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10695,56 +10712,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135330938</v>
+        <v>135325591</v>
       </c>
       <c r="B90" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>619571</v>
+        <v>619449</v>
       </c>
       <c r="R90" t="n">
-        <v>7322045</v>
+        <v>7322120</v>
       </c>
       <c r="S90" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10773,7 +10782,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10783,12 +10792,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:53</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10803,12 +10807,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10819,45 +10823,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135325591</v>
+        <v>135323146</v>
       </c>
       <c r="B91" t="n">
-        <v>57162</v>
+        <v>58136</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>619449</v>
+        <v>619591</v>
       </c>
       <c r="R91" t="n">
-        <v>7322120</v>
+        <v>7322093</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10889,7 +10893,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10899,7 +10903,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10914,12 +10918,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10930,7 +10934,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135323146</v>
+        <v>135323532</v>
       </c>
       <c r="B92" t="n">
         <v>58136</v>
@@ -10961,17 +10965,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>619591</v>
+        <v>619540</v>
       </c>
       <c r="R92" t="n">
-        <v>7322093</v>
+        <v>7322034</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11000,7 +11004,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11010,7 +11014,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11025,23 +11029,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135323532</v>
+        <v>135325587</v>
       </c>
       <c r="B93" t="n">
         <v>58136</v>
@@ -11072,17 +11072,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>619540</v>
+        <v>619517</v>
       </c>
       <c r="R93" t="n">
-        <v>7322034</v>
+        <v>7322182</v>
       </c>
       <c r="S93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11136,19 +11136,23 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135325587</v>
+        <v>135326500</v>
       </c>
       <c r="B94" t="n">
         <v>58136</v>
@@ -11176,20 +11180,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>619517</v>
+        <v>619528</v>
       </c>
       <c r="R94" t="n">
-        <v>7322182</v>
+        <v>7322006</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11218,7 +11231,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11228,7 +11241,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11243,12 +11256,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11259,7 +11272,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135326500</v>
+        <v>135330933</v>
       </c>
       <c r="B95" t="n">
         <v>58136</v>
@@ -11287,29 +11300,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>619528</v>
+        <v>619580</v>
       </c>
       <c r="R95" t="n">
-        <v>7322006</v>
+        <v>7322161</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11338,7 +11350,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11348,7 +11360,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11363,12 +11375,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11379,7 +11391,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135330933</v>
+        <v>135330937</v>
       </c>
       <c r="B96" t="n">
         <v>58136</v>
@@ -11422,13 +11434,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>619580</v>
+        <v>619572</v>
       </c>
       <c r="R96" t="n">
-        <v>7322161</v>
+        <v>7322048</v>
       </c>
       <c r="S96" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11457,7 +11469,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11467,7 +11479,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11498,10 +11510,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135330937</v>
+        <v>135321349</v>
       </c>
       <c r="B97" t="n">
-        <v>58136</v>
+        <v>78382</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11509,45 +11521,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>619572</v>
+        <v>619627</v>
       </c>
       <c r="R97" t="n">
-        <v>7322048</v>
+        <v>7322118</v>
       </c>
       <c r="S97" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11576,7 +11580,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11586,7 +11590,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11601,12 +11605,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11617,10 +11621,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135323945</v>
+        <v>135323128</v>
       </c>
       <c r="B98" t="n">
-        <v>41606</v>
+        <v>78382</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11628,42 +11632,37 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>215713</v>
+        <v>228579</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grå blåbärsfältmätare</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Entephria caesiata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Maskaure Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>619649</v>
+        <v>619549</v>
       </c>
       <c r="R98" t="n">
-        <v>7322021</v>
+        <v>7322008</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11692,7 +11691,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11702,7 +11701,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11717,57 +11716,61 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135323934</v>
+        <v>135323131</v>
       </c>
       <c r="B99" t="n">
-        <v>98066</v>
+        <v>78382</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221941</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>619430</v>
+        <v>619607</v>
       </c>
       <c r="R99" t="n">
-        <v>7322096</v>
+        <v>7322071</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11799,7 +11802,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11809,7 +11812,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11824,19 +11827,23 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135321349</v>
+        <v>135323133</v>
       </c>
       <c r="B100" t="n">
         <v>78382</v>
@@ -11867,17 +11874,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>619627</v>
+        <v>619624</v>
       </c>
       <c r="R100" t="n">
-        <v>7322118</v>
+        <v>7322126</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11931,12 +11938,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11947,7 +11954,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135323128</v>
+        <v>135326507</v>
       </c>
       <c r="B101" t="n">
         <v>78382</v>
@@ -11982,13 +11989,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>619549</v>
+        <v>619502</v>
       </c>
       <c r="R101" t="n">
-        <v>7322008</v>
+        <v>7322009</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12017,7 +12024,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12027,7 +12034,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12042,12 +12049,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12058,10 +12065,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135323131</v>
+        <v>135325592</v>
       </c>
       <c r="B102" t="n">
-        <v>78382</v>
+        <v>79963</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12069,37 +12076,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>228579</v>
+        <v>229821</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>619607</v>
+        <v>619420</v>
       </c>
       <c r="R102" t="n">
-        <v>7322071</v>
+        <v>7322103</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12128,7 +12135,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12138,7 +12145,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12153,12 +12160,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12169,10 +12176,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135323133</v>
+        <v>135326503</v>
       </c>
       <c r="B103" t="n">
-        <v>78382</v>
+        <v>79963</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12180,21 +12187,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>229821</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12204,13 +12211,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>619624</v>
+        <v>619511</v>
       </c>
       <c r="R103" t="n">
-        <v>7322126</v>
+        <v>7322024</v>
       </c>
       <c r="S103" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12239,7 +12246,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12249,7 +12256,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12264,12 +12271,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12280,10 +12287,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135326507</v>
+        <v>135321359</v>
       </c>
       <c r="B104" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12291,37 +12298,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>619502</v>
+        <v>619585</v>
       </c>
       <c r="R104" t="n">
-        <v>7322009</v>
+        <v>7322120</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12350,7 +12357,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12360,7 +12367,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12375,12 +12382,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12391,10 +12398,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135325592</v>
+        <v>135323530</v>
       </c>
       <c r="B105" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12402,37 +12409,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>619420</v>
+        <v>619609</v>
       </c>
       <c r="R105" t="n">
-        <v>7322103</v>
+        <v>7322000</v>
       </c>
       <c r="S105" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12461,7 +12468,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12471,7 +12478,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12486,26 +12493,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135326503</v>
+        <v>135329830</v>
       </c>
       <c r="B106" t="n">
-        <v>79963</v>
+        <v>79396</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,34 +12516,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>229821</v>
+        <v>260591</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>619511</v>
+        <v>619599</v>
       </c>
       <c r="R106" t="n">
-        <v>7322024</v>
+        <v>7322098</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12572,7 +12575,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12582,7 +12585,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12597,12 +12600,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12613,10 +12616,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135321359</v>
+        <v>135323529</v>
       </c>
       <c r="B107" t="n">
-        <v>79396</v>
+        <v>92366</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12624,37 +12627,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>260591</v>
+        <v>6040186</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>619585</v>
+        <v>619629</v>
       </c>
       <c r="R107" t="n">
-        <v>7322120</v>
+        <v>7321999</v>
       </c>
       <c r="S107" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12683,7 +12686,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12693,7 +12696,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12702,371 +12705,42 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
-        <v>135323530</v>
-      </c>
-      <c r="B108" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q108" t="n">
-        <v>619609</v>
-      </c>
-      <c r="R108" t="n">
-        <v>7322000</v>
-      </c>
-      <c r="S108" t="n">
-        <v>7</v>
-      </c>
-      <c r="T108" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V108" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W108" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y108" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AA108" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
-      <c r="AD108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG108" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT108" t="inlineStr"/>
-      <c r="AW108" t="inlineStr">
-        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>135329830</v>
-      </c>
-      <c r="B109" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q109" t="n">
-        <v>619599</v>
-      </c>
-      <c r="R109" t="n">
-        <v>7322098</v>
-      </c>
-      <c r="S109" t="n">
-        <v>10</v>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AA109" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
-      <c r="AD109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG109" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT109" t="inlineStr"/>
-      <c r="AW109" t="inlineStr">
-        <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>Christina Boyd</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>135323529</v>
-      </c>
-      <c r="B110" t="n">
-        <v>92366</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>6040186</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Kötticka</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Leptoporus mollis</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q110" t="n">
-        <v>619629</v>
-      </c>
-      <c r="R110" t="n">
-        <v>7321999</v>
-      </c>
-      <c r="S110" t="n">
-        <v>7</v>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AA110" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
-      <c r="AD110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF110" t="inlineStr"/>
-      <c r="AG110" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT110" t="inlineStr"/>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+      <c r="AY107" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY107"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4039,48 +4039,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135323533</v>
+        <v>135323935</v>
       </c>
       <c r="B32" t="n">
-        <v>91896</v>
+        <v>96678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3242</v>
+        <v>2166</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>619556</v>
+        <v>619433</v>
       </c>
       <c r="R32" t="n">
-        <v>7322012</v>
+        <v>7322100</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4130,84 +4130,68 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135322200</v>
+        <v>135323533</v>
       </c>
       <c r="B33" t="n">
-        <v>91937</v>
+        <v>91896</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>619552</v>
+        <v>619556</v>
       </c>
       <c r="R33" t="n">
-        <v>7322009</v>
+        <v>7322012</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4236,7 +4220,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4230,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4257,27 +4241,43 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135322204</v>
+        <v>135322200</v>
       </c>
       <c r="B34" t="n">
         <v>91937</v>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>619650</v>
+        <v>619552</v>
       </c>
       <c r="R34" t="n">
-        <v>7322160</v>
+        <v>7322009</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4388,7 +4388,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135323531</v>
+        <v>135322204</v>
       </c>
       <c r="B35" t="n">
         <v>91937</v>
@@ -4419,17 +4419,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>619624</v>
+        <v>619650</v>
       </c>
       <c r="R35" t="n">
-        <v>7322025</v>
+        <v>7322160</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4483,60 +4483,64 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135325580</v>
+        <v>135323531</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>619647</v>
+        <v>619624</v>
       </c>
       <c r="R36" t="n">
-        <v>7322062</v>
+        <v>7322025</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4565,7 +4569,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4575,7 +4579,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4590,23 +4594,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135325595</v>
+        <v>135325580</v>
       </c>
       <c r="B37" t="n">
         <v>79373</v>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>619537</v>
+        <v>619647</v>
       </c>
       <c r="R37" t="n">
-        <v>7322086</v>
+        <v>7322062</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4717,48 +4717,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135326505</v>
+        <v>135325595</v>
       </c>
       <c r="B38" t="n">
-        <v>79397</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>619507</v>
+        <v>619537</v>
       </c>
       <c r="R38" t="n">
-        <v>7322024</v>
+        <v>7322086</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4812,12 +4812,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4828,48 +4828,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135321361</v>
+        <v>135326505</v>
       </c>
       <c r="B39" t="n">
-        <v>78776</v>
+        <v>79397</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>619595</v>
+        <v>619507</v>
       </c>
       <c r="R39" t="n">
-        <v>7322144</v>
+        <v>7322024</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4923,12 +4923,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4939,7 +4939,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135321364</v>
+        <v>135321361</v>
       </c>
       <c r="B40" t="n">
         <v>78776</v>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>619580</v>
+        <v>619595</v>
       </c>
       <c r="R40" t="n">
-        <v>7322118</v>
+        <v>7322144</v>
       </c>
       <c r="S40" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,7 +5050,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135323135</v>
+        <v>135321364</v>
       </c>
       <c r="B41" t="n">
         <v>78776</v>
@@ -5081,17 +5081,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>619656</v>
+        <v>619580</v>
       </c>
       <c r="R41" t="n">
-        <v>7322137</v>
+        <v>7322118</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5145,12 +5145,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5161,7 +5161,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135323142</v>
+        <v>135323135</v>
       </c>
       <c r="B42" t="n">
         <v>78776</v>
@@ -5196,13 +5196,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>619605</v>
+        <v>619656</v>
       </c>
       <c r="R42" t="n">
-        <v>7322191</v>
+        <v>7322137</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5272,7 +5272,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135323144</v>
+        <v>135323142</v>
       </c>
       <c r="B43" t="n">
         <v>78776</v>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>619545</v>
+        <v>619605</v>
       </c>
       <c r="R43" t="n">
-        <v>7322155</v>
+        <v>7322191</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5383,7 +5383,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135325583</v>
+        <v>135323144</v>
       </c>
       <c r="B44" t="n">
         <v>78776</v>
@@ -5414,14 +5414,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>619639</v>
+        <v>619545</v>
       </c>
       <c r="R44" t="n">
-        <v>7322093</v>
+        <v>7322155</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5478,12 +5478,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5494,7 +5494,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135326502</v>
+        <v>135325583</v>
       </c>
       <c r="B45" t="n">
         <v>78776</v>
@@ -5525,17 +5525,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>619511</v>
+        <v>619639</v>
       </c>
       <c r="R45" t="n">
-        <v>7322024</v>
+        <v>7322093</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5589,12 +5589,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5605,7 +5605,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135329821</v>
+        <v>135326502</v>
       </c>
       <c r="B46" t="n">
         <v>78776</v>
@@ -5636,17 +5636,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>619634</v>
+        <v>619511</v>
       </c>
       <c r="R46" t="n">
-        <v>7321974</v>
+        <v>7322024</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5700,12 +5700,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5716,7 +5716,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135329832</v>
+        <v>135329821</v>
       </c>
       <c r="B47" t="n">
         <v>78776</v>
@@ -5751,13 +5751,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>619546</v>
+        <v>619634</v>
       </c>
       <c r="R47" t="n">
-        <v>7322084</v>
+        <v>7321974</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5827,7 +5827,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135330930</v>
+        <v>135329832</v>
       </c>
       <c r="B48" t="n">
         <v>78776</v>
@@ -5858,17 +5858,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>619612</v>
+        <v>619546</v>
       </c>
       <c r="R48" t="n">
-        <v>7322185</v>
+        <v>7322084</v>
       </c>
       <c r="S48" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5922,12 +5922,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5938,10 +5938,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135323129</v>
+        <v>135330930</v>
       </c>
       <c r="B49" t="n">
-        <v>83358</v>
+        <v>78776</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5949,37 +5949,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>619604</v>
+        <v>619612</v>
       </c>
       <c r="R49" t="n">
-        <v>7322043</v>
+        <v>7322185</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6033,12 +6033,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6049,7 +6049,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135325571</v>
+        <v>135323129</v>
       </c>
       <c r="B50" t="n">
         <v>83358</v>
@@ -6080,17 +6080,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>619631</v>
+        <v>619604</v>
       </c>
       <c r="R50" t="n">
-        <v>7322000</v>
+        <v>7322043</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6144,12 +6144,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6160,7 +6160,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135325584</v>
+        <v>135325571</v>
       </c>
       <c r="B51" t="n">
         <v>83358</v>
@@ -6195,13 +6195,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>619575</v>
+        <v>619631</v>
       </c>
       <c r="R51" t="n">
-        <v>7322155</v>
+        <v>7322000</v>
       </c>
       <c r="S51" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6271,7 +6271,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135325589</v>
+        <v>135325584</v>
       </c>
       <c r="B52" t="n">
         <v>83358</v>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>619490</v>
+        <v>619575</v>
       </c>
       <c r="R52" t="n">
-        <v>7322171</v>
+        <v>7322155</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6382,10 +6382,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135321549</v>
+        <v>135325589</v>
       </c>
       <c r="B53" t="n">
-        <v>79992</v>
+        <v>83358</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6393,37 +6393,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>619576</v>
+        <v>619490</v>
       </c>
       <c r="R53" t="n">
-        <v>7322127</v>
+        <v>7322171</v>
       </c>
       <c r="S53" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6477,12 +6477,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -6493,7 +6493,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135322202</v>
+        <v>135321549</v>
       </c>
       <c r="B54" t="n">
         <v>79992</v>
@@ -6524,17 +6524,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>619550</v>
+        <v>619576</v>
       </c>
       <c r="R54" t="n">
-        <v>7322004</v>
+        <v>7322127</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6588,12 +6588,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6604,7 +6604,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135322205</v>
+        <v>135322202</v>
       </c>
       <c r="B55" t="n">
         <v>79992</v>
@@ -6639,10 +6639,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>619648</v>
+        <v>619550</v>
       </c>
       <c r="R55" t="n">
-        <v>7322202</v>
+        <v>7322004</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6715,7 +6715,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135323132</v>
+        <v>135322205</v>
       </c>
       <c r="B56" t="n">
         <v>79992</v>
@@ -6746,17 +6746,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>619609</v>
+        <v>619648</v>
       </c>
       <c r="R56" t="n">
-        <v>7322073</v>
+        <v>7322202</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6810,12 +6810,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6826,7 +6826,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135323145</v>
+        <v>135323132</v>
       </c>
       <c r="B57" t="n">
         <v>79992</v>
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>619557</v>
+        <v>619609</v>
       </c>
       <c r="R57" t="n">
-        <v>7322144</v>
+        <v>7322073</v>
       </c>
       <c r="S57" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6937,7 +6937,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135325572</v>
+        <v>135323145</v>
       </c>
       <c r="B58" t="n">
         <v>79992</v>
@@ -6968,17 +6968,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>619648</v>
+        <v>619557</v>
       </c>
       <c r="R58" t="n">
-        <v>7321997</v>
+        <v>7322144</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7032,12 +7032,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -7048,7 +7048,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135325593</v>
+        <v>135325572</v>
       </c>
       <c r="B59" t="n">
         <v>79992</v>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>619420</v>
+        <v>619648</v>
       </c>
       <c r="R59" t="n">
-        <v>7322107</v>
+        <v>7321997</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7159,7 +7159,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135325594</v>
+        <v>135325593</v>
       </c>
       <c r="B60" t="n">
         <v>79992</v>
@@ -7194,13 +7194,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>619516</v>
+        <v>619420</v>
       </c>
       <c r="R60" t="n">
-        <v>7322084</v>
+        <v>7322107</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7270,7 +7270,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135326504</v>
+        <v>135325594</v>
       </c>
       <c r="B61" t="n">
         <v>79992</v>
@@ -7301,17 +7301,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>619507</v>
+        <v>619516</v>
       </c>
       <c r="R61" t="n">
-        <v>7322024</v>
+        <v>7322084</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7365,12 +7365,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -7381,7 +7381,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135329819</v>
+        <v>135326504</v>
       </c>
       <c r="B62" t="n">
         <v>79992</v>
@@ -7412,17 +7412,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>619650</v>
+        <v>619507</v>
       </c>
       <c r="R62" t="n">
-        <v>7321988</v>
+        <v>7322024</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7476,12 +7476,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -7492,7 +7492,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135329831</v>
+        <v>135329819</v>
       </c>
       <c r="B63" t="n">
         <v>79992</v>
@@ -7527,13 +7527,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>619545</v>
+        <v>619650</v>
       </c>
       <c r="R63" t="n">
-        <v>7322092</v>
+        <v>7321988</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7603,48 +7603,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135325590</v>
+        <v>135329831</v>
       </c>
       <c r="B64" t="n">
-        <v>80500</v>
+        <v>79992</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>619458</v>
+        <v>619545</v>
       </c>
       <c r="R64" t="n">
-        <v>7322119</v>
+        <v>7322092</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7698,12 +7698,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7714,45 +7714,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135321366</v>
+        <v>135325590</v>
       </c>
       <c r="B65" t="n">
-        <v>78377</v>
+        <v>80500</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6487</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>619580</v>
+        <v>619458</v>
       </c>
       <c r="R65" t="n">
-        <v>7322117</v>
+        <v>7322119</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7809,12 +7809,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7825,7 +7825,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135323134</v>
+        <v>135321366</v>
       </c>
       <c r="B66" t="n">
         <v>78377</v>
@@ -7856,17 +7856,17 @@
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>619656</v>
+        <v>619580</v>
       </c>
       <c r="R66" t="n">
-        <v>7322136</v>
+        <v>7322117</v>
       </c>
       <c r="S66" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7920,12 +7920,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7936,7 +7936,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135323141</v>
+        <v>135323134</v>
       </c>
       <c r="B67" t="n">
         <v>78377</v>
@@ -7971,13 +7971,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>619605</v>
+        <v>619656</v>
       </c>
       <c r="R67" t="n">
-        <v>7322191</v>
+        <v>7322136</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8047,7 +8047,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135325582</v>
+        <v>135323141</v>
       </c>
       <c r="B68" t="n">
         <v>78377</v>
@@ -8078,17 +8078,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>619634</v>
+        <v>619605</v>
       </c>
       <c r="R68" t="n">
-        <v>7322092</v>
+        <v>7322191</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8127,7 +8127,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8142,12 +8142,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8158,7 +8158,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135326506</v>
+        <v>135325582</v>
       </c>
       <c r="B69" t="n">
         <v>78377</v>
@@ -8189,17 +8189,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>619505</v>
+        <v>619634</v>
       </c>
       <c r="R69" t="n">
-        <v>7322017</v>
+        <v>7322092</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8253,12 +8253,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -8269,10 +8269,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135321369</v>
+        <v>135326506</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>78377</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8280,45 +8280,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>619598</v>
+        <v>619505</v>
       </c>
       <c r="R70" t="n">
-        <v>7322108</v>
+        <v>7322017</v>
       </c>
       <c r="S70" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8347,7 +8339,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8357,12 +8349,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack.</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8377,12 +8364,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8393,7 +8380,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135321371</v>
+        <v>135321369</v>
       </c>
       <c r="B71" t="n">
         <v>57975</v>
@@ -8436,13 +8423,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>619575</v>
+        <v>619598</v>
       </c>
       <c r="R71" t="n">
-        <v>7322044</v>
+        <v>7322108</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8471,7 +8458,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8481,7 +8468,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
@@ -8517,7 +8504,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135323143</v>
+        <v>135321371</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -8546,21 +8533,24 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>619588</v>
+        <v>619575</v>
       </c>
       <c r="R72" t="n">
-        <v>7322173</v>
+        <v>7322044</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8592,7 +8582,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8602,7 +8592,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8617,12 +8612,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8633,7 +8628,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135323524</v>
+        <v>135323143</v>
       </c>
       <c r="B73" t="n">
         <v>57975</v>
@@ -8662,16 +8657,21 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>619644</v>
+        <v>619588</v>
       </c>
       <c r="R73" t="n">
-        <v>7321971</v>
+        <v>7322173</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8713,12 +8713,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:09</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8733,19 +8728,23 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135326508</v>
+        <v>135323524</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8774,24 +8773,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>619441</v>
+        <v>619644</v>
       </c>
       <c r="R74" t="n">
-        <v>7322009</v>
+        <v>7321971</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8820,7 +8814,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8830,12 +8824,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på gran.</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8850,23 +8844,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135326509</v>
+        <v>135326508</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8897,7 +8887,7 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8906,10 +8896,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>619463</v>
+        <v>619441</v>
       </c>
       <c r="R75" t="n">
-        <v>7321984</v>
+        <v>7322009</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8941,7 +8931,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8951,12 +8941,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Ringhack på gran.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8987,7 +8977,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135326510</v>
+        <v>135326509</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -9027,10 +9017,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>619498</v>
+        <v>619463</v>
       </c>
       <c r="R76" t="n">
-        <v>7321987</v>
+        <v>7321984</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9062,7 +9052,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9072,7 +9062,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
@@ -9108,7 +9098,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135329836</v>
+        <v>135326510</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -9137,16 +9127,21 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>619599</v>
+        <v>619498</v>
       </c>
       <c r="R77" t="n">
-        <v>7321991</v>
+        <v>7321987</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9178,7 +9173,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9188,12 +9183,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9208,12 +9203,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -9224,7 +9219,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135330913</v>
+        <v>135329836</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -9253,27 +9248,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>619674</v>
+        <v>619599</v>
       </c>
       <c r="R78" t="n">
-        <v>7321952</v>
+        <v>7321991</v>
       </c>
       <c r="S78" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9302,7 +9289,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9312,12 +9299,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9332,12 +9319,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -9348,7 +9335,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135330918</v>
+        <v>135330913</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -9381,7 +9368,7 @@
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -9391,13 +9378,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>619657</v>
+        <v>619674</v>
       </c>
       <c r="R79" t="n">
-        <v>7322019</v>
+        <v>7321952</v>
       </c>
       <c r="S79" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9426,7 +9413,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9436,12 +9423,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9472,7 +9459,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135330920</v>
+        <v>135330918</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -9505,7 +9492,7 @@
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -9515,13 +9502,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>619636</v>
+        <v>619657</v>
       </c>
       <c r="R80" t="n">
-        <v>7322057</v>
+        <v>7322019</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9550,7 +9537,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9560,12 +9547,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Spår från födosök</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9596,7 +9583,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135330921</v>
+        <v>135330920</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -9639,13 +9626,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>619615</v>
+        <v>619636</v>
       </c>
       <c r="R81" t="n">
-        <v>7322104</v>
+        <v>7322057</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9674,7 +9661,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9684,12 +9671,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Spår från födosök</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9720,7 +9707,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135330922</v>
+        <v>135330921</v>
       </c>
       <c r="B82" t="n">
         <v>57975</v>
@@ -9753,7 +9740,7 @@
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
@@ -9763,10 +9750,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>619616</v>
+        <v>619615</v>
       </c>
       <c r="R82" t="n">
-        <v>7322103</v>
+        <v>7322104</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9798,7 +9785,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9808,12 +9795,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9844,7 +9831,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135330925</v>
+        <v>135330922</v>
       </c>
       <c r="B83" t="n">
         <v>57975</v>
@@ -9887,13 +9874,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>619617</v>
+        <v>619616</v>
       </c>
       <c r="R83" t="n">
-        <v>7322138</v>
+        <v>7322103</v>
       </c>
       <c r="S83" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9922,7 +9909,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9932,7 +9919,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
@@ -9968,7 +9955,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135330926</v>
+        <v>135330925</v>
       </c>
       <c r="B84" t="n">
         <v>57975</v>
@@ -10001,7 +9988,7 @@
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
@@ -10011,13 +9998,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>619652</v>
+        <v>619617</v>
       </c>
       <c r="R84" t="n">
-        <v>7322160</v>
+        <v>7322138</v>
       </c>
       <c r="S84" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10046,7 +10033,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10056,12 +10043,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10092,7 +10079,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135330929</v>
+        <v>135330926</v>
       </c>
       <c r="B85" t="n">
         <v>57975</v>
@@ -10135,13 +10122,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>619619</v>
+        <v>619652</v>
       </c>
       <c r="R85" t="n">
-        <v>7322169</v>
+        <v>7322160</v>
       </c>
       <c r="S85" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10170,7 +10157,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10180,7 +10167,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
@@ -10216,7 +10203,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135330931</v>
+        <v>135330929</v>
       </c>
       <c r="B86" t="n">
         <v>57975</v>
@@ -10249,7 +10236,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -10259,13 +10246,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>619590</v>
+        <v>619619</v>
       </c>
       <c r="R86" t="n">
-        <v>7322174</v>
+        <v>7322169</v>
       </c>
       <c r="S86" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10294,7 +10281,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10304,12 +10291,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10340,7 +10327,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135330935</v>
+        <v>135330931</v>
       </c>
       <c r="B87" t="n">
         <v>57975</v>
@@ -10383,13 +10370,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>619577</v>
+        <v>619590</v>
       </c>
       <c r="R87" t="n">
-        <v>7322144</v>
+        <v>7322174</v>
       </c>
       <c r="S87" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10418,7 +10405,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10428,7 +10415,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -10464,7 +10451,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135330936</v>
+        <v>135330935</v>
       </c>
       <c r="B88" t="n">
         <v>57975</v>
@@ -10507,13 +10494,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>619598</v>
+        <v>619577</v>
       </c>
       <c r="R88" t="n">
-        <v>7322107</v>
+        <v>7322144</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10542,7 +10529,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10552,7 +10539,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
@@ -10588,7 +10575,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135330938</v>
+        <v>135330936</v>
       </c>
       <c r="B89" t="n">
         <v>57975</v>
@@ -10631,13 +10618,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>619571</v>
+        <v>619598</v>
       </c>
       <c r="R89" t="n">
-        <v>7322045</v>
+        <v>7322107</v>
       </c>
       <c r="S89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10666,7 +10653,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10676,7 +10663,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10712,48 +10699,56 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135325591</v>
+        <v>135330938</v>
       </c>
       <c r="B90" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>619449</v>
+        <v>619571</v>
       </c>
       <c r="R90" t="n">
-        <v>7322120</v>
+        <v>7322045</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10782,7 +10777,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10792,7 +10787,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10807,12 +10807,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -10823,45 +10823,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135323146</v>
+        <v>135325591</v>
       </c>
       <c r="B91" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>619591</v>
+        <v>619449</v>
       </c>
       <c r="R91" t="n">
-        <v>7322093</v>
+        <v>7322120</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10918,12 +10918,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -10934,7 +10934,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135323532</v>
+        <v>135323146</v>
       </c>
       <c r="B92" t="n">
         <v>58136</v>
@@ -10965,17 +10965,17 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>619540</v>
+        <v>619591</v>
       </c>
       <c r="R92" t="n">
-        <v>7322034</v>
+        <v>7322093</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11029,19 +11029,23 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135325587</v>
+        <v>135323532</v>
       </c>
       <c r="B93" t="n">
         <v>58136</v>
@@ -11072,17 +11076,17 @@
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>619517</v>
+        <v>619540</v>
       </c>
       <c r="R93" t="n">
-        <v>7322182</v>
+        <v>7322034</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11111,7 +11115,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11121,7 +11125,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11136,23 +11140,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135326500</v>
+        <v>135325587</v>
       </c>
       <c r="B94" t="n">
         <v>58136</v>
@@ -11180,29 +11180,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>619528</v>
+        <v>619517</v>
       </c>
       <c r="R94" t="n">
-        <v>7322006</v>
+        <v>7322182</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11231,7 +11222,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11241,7 +11232,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11256,12 +11247,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11272,7 +11263,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135330933</v>
+        <v>135326500</v>
       </c>
       <c r="B95" t="n">
         <v>58136</v>
@@ -11300,28 +11291,29 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>619580</v>
+        <v>619528</v>
       </c>
       <c r="R95" t="n">
-        <v>7322161</v>
+        <v>7322006</v>
       </c>
       <c r="S95" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11350,7 +11342,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11360,7 +11352,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11375,12 +11367,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11391,7 +11383,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135330937</v>
+        <v>135330933</v>
       </c>
       <c r="B96" t="n">
         <v>58136</v>
@@ -11434,13 +11426,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>619572</v>
+        <v>619580</v>
       </c>
       <c r="R96" t="n">
-        <v>7322048</v>
+        <v>7322161</v>
       </c>
       <c r="S96" t="n">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11469,7 +11461,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11479,7 +11471,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11510,10 +11502,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135321349</v>
+        <v>135330937</v>
       </c>
       <c r="B97" t="n">
-        <v>78382</v>
+        <v>58136</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11521,37 +11513,45 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs + Skornjamyran, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>619627</v>
+        <v>619572</v>
       </c>
       <c r="R97" t="n">
-        <v>7322118</v>
+        <v>7322048</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11605,12 +11605,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -11621,10 +11621,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135323128</v>
+        <v>135336188</v>
       </c>
       <c r="B98" t="n">
-        <v>78382</v>
+        <v>41606</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11632,37 +11632,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228579</v>
+        <v>215713</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Grå blåbärsfältmätare</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Entephria caesiata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>619549</v>
+        <v>619649</v>
       </c>
       <c r="R98" t="n">
-        <v>7322008</v>
+        <v>7322021</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11691,7 +11696,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11701,7 +11706,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11716,12 +11721,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11732,45 +11737,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135323131</v>
+        <v>135323934</v>
       </c>
       <c r="B99" t="n">
-        <v>78382</v>
+        <v>98066</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228579</v>
+        <v>221941</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>619607</v>
+        <v>619430</v>
       </c>
       <c r="R99" t="n">
-        <v>7322071</v>
+        <v>7322096</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11802,7 +11807,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11812,7 +11817,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11827,12 +11832,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -11843,7 +11848,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135323133</v>
+        <v>135321349</v>
       </c>
       <c r="B100" t="n">
         <v>78382</v>
@@ -11874,17 +11879,17 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Uddnäs, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>619624</v>
+        <v>619627</v>
       </c>
       <c r="R100" t="n">
-        <v>7322126</v>
+        <v>7322118</v>
       </c>
       <c r="S100" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11938,12 +11943,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -11954,7 +11959,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135326507</v>
+        <v>135323128</v>
       </c>
       <c r="B101" t="n">
         <v>78382</v>
@@ -11989,13 +11994,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>619502</v>
+        <v>619549</v>
       </c>
       <c r="R101" t="n">
-        <v>7322009</v>
+        <v>7322008</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12024,7 +12029,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12034,7 +12039,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12049,12 +12054,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12065,10 +12070,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135325592</v>
+        <v>135323131</v>
       </c>
       <c r="B102" t="n">
-        <v>79963</v>
+        <v>78382</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12076,37 +12081,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>229821</v>
+        <v>228579</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>619420</v>
+        <v>619607</v>
       </c>
       <c r="R102" t="n">
-        <v>7322103</v>
+        <v>7322071</v>
       </c>
       <c r="S102" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12135,7 +12140,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12145,7 +12150,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12160,12 +12165,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jörgen Sundin</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12176,10 +12181,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135326503</v>
+        <v>135323133</v>
       </c>
       <c r="B103" t="n">
-        <v>79963</v>
+        <v>78382</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12187,21 +12192,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229821</v>
+        <v>228579</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12211,13 +12216,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>619511</v>
+        <v>619624</v>
       </c>
       <c r="R103" t="n">
-        <v>7322024</v>
+        <v>7322126</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12246,7 +12251,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12256,7 +12261,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12271,12 +12276,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12287,10 +12292,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135321359</v>
+        <v>135326507</v>
       </c>
       <c r="B104" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12298,37 +12303,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>619585</v>
+        <v>619502</v>
       </c>
       <c r="R104" t="n">
-        <v>7322120</v>
+        <v>7322009</v>
       </c>
       <c r="S104" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12357,7 +12362,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12367,7 +12372,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12382,12 +12387,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12398,10 +12403,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135323530</v>
+        <v>135325592</v>
       </c>
       <c r="B105" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12409,37 +12414,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Ons Gr 3_Maskaure Uddnäs + Skornjamyran_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>619609</v>
+        <v>619420</v>
       </c>
       <c r="R105" t="n">
-        <v>7322000</v>
+        <v>7322103</v>
       </c>
       <c r="S105" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12468,7 +12473,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12478,7 +12483,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12493,22 +12498,26 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Jörgen Sundin</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY105" t="inlineStr"/>
+          <t>Jörgen Sundin</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135329830</v>
+        <v>135326503</v>
       </c>
       <c r="B106" t="n">
-        <v>79396</v>
+        <v>79963</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12516,34 +12525,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs, Pi lm</t>
+          <t>Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>619599</v>
+        <v>619511</v>
       </c>
       <c r="R106" t="n">
-        <v>7322098</v>
+        <v>7322024</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12575,7 +12584,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12585,7 +12594,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12600,12 +12609,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -12616,10 +12625,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135323529</v>
+        <v>135321359</v>
       </c>
       <c r="B107" t="n">
-        <v>92366</v>
+        <v>79396</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12627,37 +12636,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6040186</v>
+        <v>260591</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+          <t>Maskaure Uddnäs, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>619629</v>
+        <v>619585</v>
       </c>
       <c r="R107" t="n">
-        <v>7321999</v>
+        <v>7322120</v>
       </c>
       <c r="S107" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12686,7 +12695,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12696,7 +12705,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12705,42 +12714,371 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>135323530</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>619609</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7322000</v>
+      </c>
+      <c r="S108" t="n">
+        <v>7</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
+      <c r="AX108" t="inlineStr">
         <is>
           <t>Cecilia Goldkuhl</t>
         </is>
       </c>
-      <c r="AY107" t="inlineStr"/>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>135329830</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>619599</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7322098</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>135323529</v>
+      </c>
+      <c r="B110" t="n">
+        <v>92366</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Maskaure Uddnäs + Skornjamyran_topo, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>619629</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7321999</v>
+      </c>
+      <c r="S110" t="n">
+        <v>7</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -4139,7 +4139,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka, Johan Råghall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -6149,7 +6149,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -12059,7 +12059,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, per-erik mukka, Laura de Jong, Cecilia Goldkuhl, Martin Axegård, Johan Råghall</t>
+          <t>Cajsa Björkén, Jörgen Sundin, Klas Magnusson, anders tedeholm, Johan Råghall, Martin Axegård, Cecilia Goldkuhl, Laura de Jong, per-erik mukka</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AZ110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323140</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321345</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322203</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323127</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323130</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1445,6 +1480,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323526</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323528</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1683,6 +1728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326359</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330917</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1905,6 +1960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325581</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325575</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2132,6 +2197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329802</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2243,6 +2313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330939</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2354,6 +2429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323123</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2465,6 +2545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329816</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2572,6 +2657,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323527</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2683,6 +2773,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325573</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2794,6 +2889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326358</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2905,6 +3005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326498</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3016,6 +3121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330914</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3127,6 +3237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330915</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3238,6 +3353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330924</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3349,6 +3469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321343</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3465,6 +3590,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329804</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3576,6 +3706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325577</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3687,6 +3822,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325579</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3798,6 +3938,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325586</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3909,6 +4054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326499</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4036,6 +4186,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323535</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4147,6 +4302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323935</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4274,6 +4434,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323533</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4385,6 +4550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322200</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4496,6 +4666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322204</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4603,6 +4778,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323531</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4714,6 +4894,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325580</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4825,6 +5010,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325595</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4936,6 +5126,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326505</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5047,6 +5242,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321361</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5158,6 +5358,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321364</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5269,6 +5474,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323135</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5380,6 +5590,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323142</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5491,6 +5706,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323144</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5602,6 +5822,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325583</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5713,6 +5938,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326502</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5824,6 +6054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329821</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5935,6 +6170,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329832</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6046,6 +6286,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330930</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6157,6 +6402,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323129</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6268,6 +6518,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325571</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6379,6 +6634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325584</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6490,6 +6750,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325589</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6601,6 +6866,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321549</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6712,6 +6982,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322202</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6823,6 +7098,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135322205</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6934,6 +7214,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323132</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7045,6 +7330,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323145</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7156,6 +7446,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325572</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7267,6 +7562,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325593</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7378,6 +7678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325594</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7489,6 +7794,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326504</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7600,6 +7910,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329819</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7711,6 +8026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329831</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7822,6 +8142,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325590</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7933,6 +8258,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321366</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8044,6 +8374,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323134</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8155,6 +8490,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323141</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8266,6 +8606,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325582</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8377,6 +8722,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326506</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8501,6 +8851,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321369</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8625,6 +8980,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321371</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8741,6 +9101,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323143</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8853,6 +9218,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323524</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8974,6 +9344,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326508</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9095,6 +9470,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326509</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9216,6 +9596,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326510</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9332,6 +9717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329836</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9456,6 +9846,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330913</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9580,6 +9975,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330918</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9704,6 +10104,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330920</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9828,6 +10233,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330921</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9952,6 +10362,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330922</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10076,6 +10491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330925</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10200,6 +10620,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330926</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10324,6 +10749,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330929</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10448,6 +10878,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330931</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10572,6 +11007,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330935</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10696,6 +11136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330936</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10820,6 +11265,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330938</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10931,6 +11381,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325591</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11042,6 +11497,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323146</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11149,6 +11609,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323532</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11260,6 +11725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325587</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11380,6 +11850,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326500</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11499,6 +11974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330933</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11618,6 +12098,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135330937</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11734,6 +12219,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135336188</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11845,6 +12335,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323934</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11956,6 +12451,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321349</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12067,6 +12567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323128</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12178,6 +12683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323131</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12289,6 +12799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323133</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12400,6 +12915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326507</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12511,6 +13031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325592</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12622,6 +13147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135326503</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12733,6 +13263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135321359</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12840,6 +13375,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323530</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12951,6 +13491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135329830</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13079,8 +13624,124 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135323529</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323126</v>
       </c>
       <c r="B2" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135323140</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135321345</v>
       </c>
       <c r="B4" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135322203</v>
       </c>
       <c r="B5" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135323127</v>
       </c>
       <c r="B6" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135323130</v>
       </c>
       <c r="B7" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135323526</v>
       </c>
       <c r="B8" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135323528</v>
       </c>
       <c r="B9" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135326359</v>
       </c>
       <c r="B10" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135330917</v>
       </c>
       <c r="B11" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135325581</v>
       </c>
       <c r="B12" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135325575</v>
       </c>
       <c r="B13" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135329802</v>
       </c>
       <c r="B14" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>135330939</v>
       </c>
       <c r="B15" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135323123</v>
       </c>
       <c r="B16" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135329816</v>
       </c>
       <c r="B17" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>135323527</v>
       </c>
       <c r="B18" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>135325573</v>
       </c>
       <c r="B19" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>135326358</v>
       </c>
       <c r="B20" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>135326498</v>
       </c>
       <c r="B21" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>135330914</v>
       </c>
       <c r="B22" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135330915</v>
       </c>
       <c r="B23" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135330924</v>
       </c>
       <c r="B24" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135321343</v>
       </c>
       <c r="B25" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135329804</v>
       </c>
       <c r="B26" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>135325577</v>
       </c>
       <c r="B27" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>135325579</v>
       </c>
       <c r="B28" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>135325586</v>
       </c>
       <c r="B29" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135326499</v>
       </c>
       <c r="B30" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>135323535</v>
       </c>
       <c r="B31" t="n">
-        <v>92318</v>
+        <v>92360</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>135323935</v>
       </c>
       <c r="B32" t="n">
-        <v>96678</v>
+        <v>96722</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>135323533</v>
       </c>
       <c r="B33" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>135322200</v>
       </c>
       <c r="B34" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135322204</v>
       </c>
       <c r="B35" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>135323531</v>
       </c>
       <c r="B36" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135325580</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>135325595</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>135326505</v>
       </c>
       <c r="B39" t="n">
-        <v>79397</v>
+        <v>79435</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>135321361</v>
       </c>
       <c r="B40" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>135321364</v>
       </c>
       <c r="B41" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135323135</v>
       </c>
       <c r="B42" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>135323142</v>
       </c>
       <c r="B43" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135323144</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>135325583</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>135326502</v>
       </c>
       <c r="B46" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135329821</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>135329832</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>135330930</v>
       </c>
       <c r="B49" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>135323129</v>
       </c>
       <c r="B50" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>135325571</v>
       </c>
       <c r="B51" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135325584</v>
       </c>
       <c r="B52" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>135325589</v>
       </c>
       <c r="B53" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>135321549</v>
       </c>
       <c r="B54" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>135322202</v>
       </c>
       <c r="B55" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>135322205</v>
       </c>
       <c r="B56" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>135323132</v>
       </c>
       <c r="B57" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>135323145</v>
       </c>
       <c r="B58" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>135325572</v>
       </c>
       <c r="B59" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>135325593</v>
       </c>
       <c r="B60" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135325594</v>
       </c>
       <c r="B61" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>135326504</v>
       </c>
       <c r="B62" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135329819</v>
       </c>
       <c r="B63" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>135329831</v>
       </c>
       <c r="B64" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>135325590</v>
       </c>
       <c r="B65" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>135321366</v>
       </c>
       <c r="B66" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>135323134</v>
       </c>
       <c r="B67" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135323141</v>
       </c>
       <c r="B68" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135325582</v>
       </c>
       <c r="B69" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>135326506</v>
       </c>
       <c r="B70" t="n">
-        <v>78377</v>
+        <v>78415</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>135321369</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>135321371</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>135323143</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>135323524</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>135326508</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>135326509</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>135326510</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>135329836</v>
       </c>
       <c r="B78" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>135330913</v>
       </c>
       <c r="B79" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9857,7 +9857,7 @@
         <v>135330918</v>
       </c>
       <c r="B80" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>135330920</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10115,7 +10115,7 @@
         <v>135330921</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>135330922</v>
       </c>
       <c r="B83" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>135330925</v>
       </c>
       <c r="B84" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>135330926</v>
       </c>
       <c r="B85" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>135330929</v>
       </c>
       <c r="B86" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>135330931</v>
       </c>
       <c r="B87" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>135330935</v>
       </c>
       <c r="B88" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>135330936</v>
       </c>
       <c r="B89" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>135330938</v>
       </c>
       <c r="B90" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>135325591</v>
       </c>
       <c r="B91" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>135323146</v>
       </c>
       <c r="B92" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>135323532</v>
       </c>
       <c r="B93" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>135325587</v>
       </c>
       <c r="B94" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>135326500</v>
       </c>
       <c r="B95" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>135330933</v>
       </c>
       <c r="B96" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>135330937</v>
       </c>
       <c r="B97" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>135336188</v>
       </c>
       <c r="B98" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>135323934</v>
       </c>
       <c r="B99" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>135321349</v>
       </c>
       <c r="B100" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>135323128</v>
       </c>
       <c r="B101" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>135323131</v>
       </c>
       <c r="B102" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>135323133</v>
       </c>
       <c r="B103" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>135326507</v>
       </c>
       <c r="B104" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>135325592</v>
       </c>
       <c r="B105" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>135326503</v>
       </c>
       <c r="B106" t="n">
-        <v>79963</v>
+        <v>80001</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>135321359</v>
       </c>
       <c r="B107" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>135323530</v>
       </c>
       <c r="B108" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>135329830</v>
       </c>
       <c r="B109" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>135323529</v>
       </c>
       <c r="B110" t="n">
-        <v>92366</v>
+        <v>92408</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323126</v>
       </c>
       <c r="B2" t="n">
-        <v>92635</v>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135323140</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79104</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135321345</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135322203</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135323127</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135323130</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135323526</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135323528</v>
       </c>
       <c r="B9" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135326359</v>
       </c>
       <c r="B10" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135330917</v>
       </c>
       <c r="B11" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>135325581</v>
       </c>
       <c r="B12" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135325575</v>
       </c>
       <c r="B13" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135329802</v>
       </c>
       <c r="B14" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>135330939</v>
       </c>
       <c r="B15" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135323123</v>
       </c>
       <c r="B16" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135329816</v>
       </c>
       <c r="B17" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>135323527</v>
       </c>
       <c r="B18" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>135325573</v>
       </c>
       <c r="B19" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>135326358</v>
       </c>
       <c r="B20" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>135326498</v>
       </c>
       <c r="B21" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>135330914</v>
       </c>
       <c r="B22" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135330915</v>
       </c>
       <c r="B23" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135330924</v>
       </c>
       <c r="B24" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135321343</v>
       </c>
       <c r="B25" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135329804</v>
       </c>
       <c r="B26" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>135325577</v>
       </c>
       <c r="B27" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>135325579</v>
       </c>
       <c r="B28" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>135325586</v>
       </c>
       <c r="B29" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>135326499</v>
       </c>
       <c r="B30" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>135323535</v>
       </c>
       <c r="B31" t="n">
-        <v>92360</v>
+        <v>92387</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>135323935</v>
       </c>
       <c r="B32" t="n">
-        <v>96722</v>
+        <v>96749</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>135323533</v>
       </c>
       <c r="B33" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>135322200</v>
       </c>
       <c r="B34" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135322204</v>
       </c>
       <c r="B35" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>135323531</v>
       </c>
       <c r="B36" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>135325580</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>135325595</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>135326505</v>
       </c>
       <c r="B39" t="n">
-        <v>79435</v>
+        <v>79462</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>135321361</v>
       </c>
       <c r="B40" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>135321364</v>
       </c>
       <c r="B41" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>135323135</v>
       </c>
       <c r="B42" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>135323142</v>
       </c>
       <c r="B43" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135323144</v>
       </c>
       <c r="B44" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>135325583</v>
       </c>
       <c r="B45" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>135326502</v>
       </c>
       <c r="B46" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         <v>135329821</v>
       </c>
       <c r="B47" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>135329832</v>
       </c>
       <c r="B48" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>135330930</v>
       </c>
       <c r="B49" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>135323129</v>
       </c>
       <c r="B50" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>135325571</v>
       </c>
       <c r="B51" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>135325584</v>
       </c>
       <c r="B52" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>135325589</v>
       </c>
       <c r="B53" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>135321549</v>
       </c>
       <c r="B54" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>135322202</v>
       </c>
       <c r="B55" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>135322205</v>
       </c>
       <c r="B56" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>135323132</v>
       </c>
       <c r="B57" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>135323145</v>
       </c>
       <c r="B58" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>135325572</v>
       </c>
       <c r="B59" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>135325593</v>
       </c>
       <c r="B60" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7573,7 +7573,7 @@
         <v>135325594</v>
       </c>
       <c r="B61" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>135326504</v>
       </c>
       <c r="B62" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>135329819</v>
       </c>
       <c r="B63" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>135329831</v>
       </c>
       <c r="B64" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>135325590</v>
       </c>
       <c r="B65" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>135321366</v>
       </c>
       <c r="B66" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>135323134</v>
       </c>
       <c r="B67" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>135323141</v>
       </c>
       <c r="B68" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>135325582</v>
       </c>
       <c r="B69" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>135326506</v>
       </c>
       <c r="B70" t="n">
-        <v>78415</v>
+        <v>78442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12230,7 +12230,7 @@
         <v>135323934</v>
       </c>
       <c r="B99" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>135321349</v>
       </c>
       <c r="B100" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12462,7 +12462,7 @@
         <v>135323128</v>
       </c>
       <c r="B101" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>135323131</v>
       </c>
       <c r="B102" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>135323133</v>
       </c>
       <c r="B103" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>135326507</v>
       </c>
       <c r="B104" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>135325592</v>
       </c>
       <c r="B105" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>135326503</v>
       </c>
       <c r="B106" t="n">
-        <v>80001</v>
+        <v>80028</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>135321359</v>
       </c>
       <c r="B107" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>135323530</v>
       </c>
       <c r="B108" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>135329830</v>
       </c>
       <c r="B109" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>135323529</v>
       </c>
       <c r="B110" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135323126</v>
       </c>
       <c r="B2" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135321345</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135322203</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135323127</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135323130</v>
       </c>
       <c r="B7" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135323526</v>
       </c>
       <c r="B8" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135323528</v>
       </c>
       <c r="B9" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1623,7 +1623,7 @@
         <v>135326359</v>
       </c>
       <c r="B10" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>135330917</v>
       </c>
       <c r="B11" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>135325575</v>
       </c>
       <c r="B13" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>135329802</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>135330939</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>135323123</v>
       </c>
       <c r="B16" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>135329816</v>
       </c>
       <c r="B17" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>135323527</v>
       </c>
       <c r="B18" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>135325573</v>
       </c>
       <c r="B19" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2784,7 +2784,7 @@
         <v>135326358</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>135326498</v>
       </c>
       <c r="B21" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>135330914</v>
       </c>
       <c r="B22" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         <v>135330915</v>
       </c>
       <c r="B23" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>135330924</v>
       </c>
       <c r="B24" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135321343</v>
       </c>
       <c r="B25" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135329804</v>
       </c>
       <c r="B26" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>135323535</v>
       </c>
       <c r="B31" t="n">
-        <v>92392</v>
+        <v>92394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>135323935</v>
       </c>
       <c r="B32" t="n">
-        <v>96754</v>
+        <v>96756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>135323533</v>
       </c>
       <c r="B33" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4445,7 +4445,7 @@
         <v>135322200</v>
       </c>
       <c r="B34" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4561,7 +4561,7 @@
         <v>135322204</v>
       </c>
       <c r="B35" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>135323531</v>
       </c>
       <c r="B36" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>135323934</v>
       </c>
       <c r="B99" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>135323529</v>
       </c>
       <c r="B110" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
+          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
+          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -1836,7 +1836,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -10612,7 +10612,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -11257,7 +11257,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén</t>
+          <t>Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12327,7 +12327,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Martin Axegård, Christina Boyd, Laura de Jong, per-erik mukka, Johan Råghall, Jörgen Sundin, Cecilia Goldkuhl, Moa Turid Lövdahl, Cajsa Björkén, Elin Kannerby</t>
+          <t>Klas Magnusson, Elin Kannerby, Cajsa Björkén, Moa Turid Lövdahl, Cecilia Goldkuhl, Jörgen Sundin, Johan Råghall, per-erik mukka, Laura de Jong, Christina Boyd, Martin Axegård</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">

--- a/artfynd/A 37442-2025 artfynd.xlsx
+++ b/artfynd/A 37442-2025 artfynd.xlsx
@@ -4197,7 +4197,7 @@
         <v>135323935</v>
       </c>
       <c r="B32" t="n">
-        <v>96756</v>
+        <v>96773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>135336188</v>
       </c>
       <c r="B98" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>135323934</v>
       </c>
       <c r="B99" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
